--- a/DesignDocs/Events.xlsx
+++ b/DesignDocs/Events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cstew\source\repos\BarbarianPrince\DesignDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B753465-AF56-4922-841A-ECC1E93D026E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10652E70-FA6D-49CB-A55C-6F8451035C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{89590866-6083-4176-8CBF-8C95C9BA24C2}"/>
   </bookViews>
@@ -4751,16 +4751,6 @@
                            &lt;InlineUIContainer&gt;&lt;Image Name='WitchStart' Source='../images/Witch.gif' Height='300' Width='240'&gt;&lt;/Image&gt;&lt;/InlineUIContainer&gt;</t>
   </si>
   <si>
-    <t>&lt;Bold&gt;e073a Hostile Witch&lt;/Bold&gt;
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;Your party must escape
- &lt;InlineUIContainer&gt;&lt;Button Content='r218' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;
- immediately. Roll one die for each character in your party including yourself. 
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;If a six occurs, the character is turned into a frog and is lost. If you are turned into a frog; any frog, lover, magician, wizard, or friendly witch surviving in your party can turn you back.
-&lt;LineBreak/&gt;&lt;LineBreak/&gt;Otherwise, you remain a frog for years and lose the game. Click image to continue.
-&lt;LineBreak/&gt; &lt;LineBreak/&gt;
-                           &lt;InlineUIContainer&gt;&lt;Image Name='Witch' Source='../images/Witch.gif' Height='300' Width='240'&gt;&lt;/Image&gt;&lt;/InlineUIContainer&gt;</t>
-  </si>
-  <si>
     <t>&lt;Bold&gt;e073b Indifferent Witch&lt;/Bold&gt;
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;You pass with no incident. Click image to continue.
 &lt;LineBreak/&gt; &lt;LineBreak/&gt;
@@ -8135,6 +8125,16 @@
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;&lt;InlineUIContainer&gt;&lt;Image Name='EncounterEnd' Source='../images/FoodDeny.gif' Height='100'  Width='100'&gt; &lt;/Image&gt;&lt;/InlineUIContainer&gt; 
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;Click to allow him to join:
 &lt;LineBreak/&gt;&lt;LineBreak/&gt;&lt;InlineUIContainer&gt;&lt;Image Name='HireFreeman' Source='../images/Food.gif' Height='100'  Width='100'&gt; &lt;/Image&gt;&lt;/InlineUIContainer&gt; </t>
+  </si>
+  <si>
+    <t>&lt;Bold&gt;e073a Hostile Witch&lt;/Bold&gt;
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;Your party must escape
+ &lt;InlineUIContainer&gt;&lt;Button Content='r218' FontFamily='Courier New'  FontSize='12'&gt;&lt;/Button&gt;&lt;/InlineUIContainer&gt;
+ immediately. Roll one die for each character in your party including yourself. 
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;If a six occurs, the character is turned into a frog and is lost. If you are turned into a frog; any lover, magician, wizard, or friendly witch surviving in your party can turn you back.
+&lt;LineBreak/&gt;&lt;LineBreak/&gt;Otherwise, you remain a frog for years and lose the game. Click image to continue.
+&lt;LineBreak/&gt; &lt;LineBreak/&gt;
+                           &lt;InlineUIContainer&gt;&lt;Image Name='Witch' Source='../images/Witch.gif' Height='300' Width='240'&gt;&lt;/Image&gt;&lt;/InlineUIContainer&gt;</t>
   </si>
 </sst>
 </file>
@@ -8547,7 +8547,7 @@
         <v>254</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="142.69999999999999" x14ac:dyDescent="0.25">
@@ -8579,7 +8579,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="199.7" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
         <v>653</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="171.2" x14ac:dyDescent="0.25">
@@ -9243,7 +9243,7 @@
         <v>57</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -9467,7 +9467,7 @@
         <v>71</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -9939,7 +9939,7 @@
         <v>92</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10259,7 +10259,7 @@
         <v>169</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>852</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10267,7 +10267,7 @@
         <v>170</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10275,7 +10275,7 @@
         <v>171</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -10283,7 +10283,7 @@
         <v>113</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -10291,7 +10291,7 @@
         <v>114</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10299,7 +10299,7 @@
         <v>266</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -10307,7 +10307,7 @@
         <v>559</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10315,7 +10315,7 @@
         <v>115</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10323,7 +10323,7 @@
         <v>518</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -10331,7 +10331,7 @@
         <v>116</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10339,7 +10339,7 @@
         <v>516</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10347,7 +10347,7 @@
         <v>117</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10355,7 +10355,7 @@
         <v>519</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10363,7 +10363,7 @@
         <v>520</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10371,7 +10371,7 @@
         <v>521</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10379,7 +10379,7 @@
         <v>118</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -10387,7 +10387,7 @@
         <v>562</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10395,7 +10395,7 @@
         <v>563</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10403,7 +10403,7 @@
         <v>119</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10411,7 +10411,7 @@
         <v>555</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10419,7 +10419,7 @@
         <v>554</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10427,7 +10427,7 @@
         <v>120</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -10435,7 +10435,7 @@
         <v>172</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10443,7 +10443,7 @@
         <v>173</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -10451,7 +10451,7 @@
         <v>174</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -10459,7 +10459,7 @@
         <v>121</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -10467,7 +10467,7 @@
         <v>122</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10475,7 +10475,7 @@
         <v>517</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -10483,7 +10483,7 @@
         <v>123</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10491,7 +10491,7 @@
         <v>560</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -10499,7 +10499,7 @@
         <v>561</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10507,7 +10507,7 @@
         <v>124</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10515,7 +10515,7 @@
         <v>604</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10523,7 +10523,7 @@
         <v>125</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -10531,7 +10531,7 @@
         <v>578</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -10539,7 +10539,7 @@
         <v>126</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -10547,7 +10547,7 @@
         <v>127</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10555,7 +10555,7 @@
         <v>128</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -10563,7 +10563,7 @@
         <v>129</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10571,7 +10571,7 @@
         <v>130</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -10579,7 +10579,7 @@
         <v>131</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -10587,7 +10587,7 @@
         <v>565</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10595,7 +10595,7 @@
         <v>566</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -10603,7 +10603,7 @@
         <v>132</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10611,7 +10611,7 @@
         <v>133</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10619,7 +10619,7 @@
         <v>564</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -10627,7 +10627,7 @@
         <v>134</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10635,7 +10635,7 @@
         <v>579</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10643,7 +10643,7 @@
         <v>580</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -10651,7 +10651,7 @@
         <v>135</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -10659,7 +10659,7 @@
         <v>581</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10667,7 +10667,7 @@
         <v>136</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
         <v>137</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10683,7 +10683,7 @@
         <v>232</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10691,7 +10691,7 @@
         <v>233</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -10707,7 +10707,7 @@
         <v>234</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10715,7 +10715,7 @@
         <v>235</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -10731,7 +10731,7 @@
         <v>239</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10739,7 +10739,7 @@
         <v>240</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10747,7 +10747,7 @@
         <v>241</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10763,7 +10763,7 @@
         <v>236</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="280" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10771,7 +10771,7 @@
         <v>237</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10779,7 +10779,7 @@
         <v>238</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10787,7 +10787,7 @@
         <v>141</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10795,7 +10795,7 @@
         <v>142</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10803,7 +10803,7 @@
         <v>143</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -10811,7 +10811,7 @@
         <v>144</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10819,7 +10819,7 @@
         <v>242</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -10827,7 +10827,7 @@
         <v>145</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10835,7 +10835,7 @@
         <v>146</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10843,7 +10843,7 @@
         <v>147</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10851,7 +10851,7 @@
         <v>148</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -10859,7 +10859,7 @@
         <v>149</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="292" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -10867,7 +10867,7 @@
         <v>592</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10875,7 +10875,7 @@
         <v>591</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="294" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -10883,7 +10883,7 @@
         <v>593</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="295" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10891,7 +10891,7 @@
         <v>150</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="296" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10899,7 +10899,7 @@
         <v>594</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="297" spans="1:2" ht="225" x14ac:dyDescent="0.25">
@@ -10907,7 +10907,7 @@
         <v>151</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10915,7 +10915,7 @@
         <v>243</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -10923,7 +10923,7 @@
         <v>244</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10931,7 +10931,7 @@
         <v>245</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -10939,7 +10939,7 @@
         <v>152</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10947,7 +10947,7 @@
         <v>153</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -10955,7 +10955,7 @@
         <v>154</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="304" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -10963,7 +10963,7 @@
         <v>155</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="305" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -10971,7 +10971,7 @@
         <v>156</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="306" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -10987,7 +10987,7 @@
         <v>246</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="308" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -10995,7 +10995,7 @@
         <v>247</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="309" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -11003,7 +11003,7 @@
         <v>248</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="310" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11019,7 +11019,7 @@
         <v>159</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="312" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11027,7 +11027,7 @@
         <v>160</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="313" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -11035,7 +11035,7 @@
         <v>161</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="314" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -11043,7 +11043,7 @@
         <v>162</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="315" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11051,7 +11051,7 @@
         <v>587</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="316" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11059,7 +11059,7 @@
         <v>588</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="317" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11067,7 +11067,7 @@
         <v>589</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="318" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -11075,7 +11075,7 @@
         <v>163</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="319" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11083,7 +11083,7 @@
         <v>164</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="320" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11091,7 +11091,7 @@
         <v>175</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11099,7 +11099,7 @@
         <v>176</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="322" spans="1:2" ht="390" x14ac:dyDescent="0.25">
@@ -11107,7 +11107,7 @@
         <v>177</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -11123,7 +11123,7 @@
         <v>411</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11131,7 +11131,7 @@
         <v>412</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="326" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -11139,7 +11139,7 @@
         <v>413</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="327" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -11147,7 +11147,7 @@
         <v>414</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="328" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11155,7 +11155,7 @@
         <v>415</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="329" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11163,7 +11163,7 @@
         <v>600</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="330" spans="1:2" ht="390" x14ac:dyDescent="0.25">
@@ -11171,7 +11171,7 @@
         <v>178</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="331" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -11187,7 +11187,7 @@
         <v>423</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="333" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11195,7 +11195,7 @@
         <v>424</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="334" spans="1:2" ht="315" x14ac:dyDescent="0.25">
@@ -11203,7 +11203,7 @@
         <v>179</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="335" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -11211,7 +11211,7 @@
         <v>249</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="336" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -11219,7 +11219,7 @@
         <v>250</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="337" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -11227,7 +11227,7 @@
         <v>251</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="338" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11235,7 +11235,7 @@
         <v>252</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="339" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -11243,7 +11243,7 @@
         <v>253</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="340" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -11251,7 +11251,7 @@
         <v>538</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="341" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -11259,7 +11259,7 @@
         <v>539</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="342" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11267,7 +11267,7 @@
         <v>180</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="343" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11275,7 +11275,7 @@
         <v>181</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="344" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11283,7 +11283,7 @@
         <v>384</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="345" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -11299,7 +11299,7 @@
         <v>609</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11307,7 +11307,7 @@
         <v>183</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="348" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -11315,7 +11315,7 @@
         <v>184</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="349" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -11331,7 +11331,7 @@
         <v>185</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="351" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -11339,7 +11339,7 @@
         <v>186</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="352" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -11347,7 +11347,7 @@
         <v>187</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="353" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11363,7 +11363,7 @@
         <v>188</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="355" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -11371,7 +11371,7 @@
         <v>189</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="356" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11379,7 +11379,7 @@
         <v>381</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="357" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -11387,7 +11387,7 @@
         <v>382</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="358" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -11395,7 +11395,7 @@
         <v>190</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="359" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -11403,7 +11403,7 @@
         <v>191</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="360" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -11411,7 +11411,7 @@
         <v>192</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="361" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11419,7 +11419,7 @@
         <v>461</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="362" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -11427,7 +11427,7 @@
         <v>193</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="363" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -11443,7 +11443,7 @@
         <v>332</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="365" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -11451,7 +11451,7 @@
         <v>611</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="366" spans="1:2" ht="225" x14ac:dyDescent="0.25">
@@ -11459,7 +11459,7 @@
         <v>612</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="367" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11467,7 +11467,7 @@
         <v>614</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="368" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11475,7 +11475,7 @@
         <v>615</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="369" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11483,7 +11483,7 @@
         <v>616</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11491,7 +11491,7 @@
         <v>617</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="371" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11499,7 +11499,7 @@
         <v>618</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11507,7 +11507,7 @@
         <v>619</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -11515,7 +11515,7 @@
         <v>194</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="374" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -11523,7 +11523,7 @@
         <v>195</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11531,7 +11531,7 @@
         <v>607</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="376" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -11539,7 +11539,7 @@
         <v>196</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="377" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -11547,7 +11547,7 @@
         <v>327</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="378" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -11555,7 +11555,7 @@
         <v>197</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="379" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11563,7 +11563,7 @@
         <v>483</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="380" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11571,7 +11571,7 @@
         <v>198</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11579,7 +11579,7 @@
         <v>199</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -11587,7 +11587,7 @@
         <v>200</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11595,7 +11595,7 @@
         <v>201</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11603,7 +11603,7 @@
         <v>202</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -11611,7 +11611,7 @@
         <v>203</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="386" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -11659,7 +11659,7 @@
         <v>204</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11667,7 +11667,7 @@
         <v>455</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="393" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11675,7 +11675,7 @@
         <v>456</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="394" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11683,7 +11683,7 @@
         <v>457</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="395" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11691,7 +11691,7 @@
         <v>458</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -11699,7 +11699,7 @@
         <v>459</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="397" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11707,7 +11707,7 @@
         <v>460</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -11715,7 +11715,7 @@
         <v>205</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -11787,7 +11787,7 @@
         <v>207</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -11795,7 +11795,7 @@
         <v>208</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -11803,7 +11803,7 @@
         <v>209</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11811,7 +11811,7 @@
         <v>472</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11819,7 +11819,7 @@
         <v>473</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11827,7 +11827,7 @@
         <v>474</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="413" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11835,7 +11835,7 @@
         <v>475</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11843,7 +11843,7 @@
         <v>476</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -11851,7 +11851,7 @@
         <v>477</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -11859,7 +11859,7 @@
         <v>608</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="417" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -11867,7 +11867,7 @@
         <v>210</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="418" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11875,7 +11875,7 @@
         <v>465</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="419" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11883,7 +11883,7 @@
         <v>466</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="420" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11891,7 +11891,7 @@
         <v>467</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="421" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11899,7 +11899,7 @@
         <v>468</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="422" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11907,7 +11907,7 @@
         <v>469</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="423" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11915,7 +11915,7 @@
         <v>470</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="424" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11923,7 +11923,7 @@
         <v>471</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="425" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -11931,7 +11931,7 @@
         <v>606</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="426" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -11939,7 +11939,7 @@
         <v>211</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="427" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -11947,7 +11947,7 @@
         <v>212</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="428" spans="1:2" ht="300" x14ac:dyDescent="0.25">
@@ -11955,7 +11955,7 @@
         <v>416</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="429" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11963,7 +11963,7 @@
         <v>417</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11971,7 +11971,7 @@
         <v>418</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="431" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -11979,7 +11979,7 @@
         <v>419</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="432" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -11987,7 +11987,7 @@
         <v>213</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="433" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -11995,7 +11995,7 @@
         <v>214</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -12003,7 +12003,7 @@
         <v>215</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="435" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12011,7 +12011,7 @@
         <v>216</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12019,7 +12019,7 @@
         <v>217</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12027,7 +12027,7 @@
         <v>218</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12035,7 +12035,7 @@
         <v>219</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12043,7 +12043,7 @@
         <v>220</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="440" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12051,7 +12051,7 @@
         <v>221</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="441" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12059,7 +12059,7 @@
         <v>222</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12067,7 +12067,7 @@
         <v>223</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="443" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -12075,7 +12075,7 @@
         <v>224</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -12083,7 +12083,7 @@
         <v>328</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12091,7 +12091,7 @@
         <v>383</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12099,7 +12099,7 @@
         <v>225</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -12107,7 +12107,7 @@
         <v>226</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="195" x14ac:dyDescent="0.25">
@@ -12115,7 +12115,7 @@
         <v>227</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="449" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -12123,7 +12123,7 @@
         <v>228</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="450" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -12131,7 +12131,7 @@
         <v>605</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="451" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12139,7 +12139,7 @@
         <v>229</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="452" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -12147,7 +12147,7 @@
         <v>230</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="453" spans="1:2" ht="225" x14ac:dyDescent="0.25">
@@ -12155,7 +12155,7 @@
         <v>231</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="454" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12163,7 +12163,7 @@
         <v>257</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="455" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -12171,7 +12171,7 @@
         <v>377</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="456" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12179,7 +12179,7 @@
         <v>378</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="457" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12187,7 +12187,7 @@
         <v>440</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="458" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12203,7 +12203,7 @@
         <v>525</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="460" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -12251,7 +12251,7 @@
         <v>590</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="466" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -12259,7 +12259,7 @@
         <v>321</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12267,7 +12267,7 @@
         <v>393</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="468" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -12275,7 +12275,7 @@
         <v>392</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="469" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12283,7 +12283,7 @@
         <v>394</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12291,7 +12291,7 @@
         <v>395</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="471" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12299,7 +12299,7 @@
         <v>396</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12307,7 +12307,7 @@
         <v>397</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="473" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12315,7 +12315,7 @@
         <v>398</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="474" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12323,7 +12323,7 @@
         <v>427</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="475" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -12331,7 +12331,7 @@
         <v>428</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="476" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12339,7 +12339,7 @@
         <v>633</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="477" spans="1:2" ht="225" x14ac:dyDescent="0.25">
@@ -12347,7 +12347,7 @@
         <v>429</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="478" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12355,7 +12355,7 @@
         <v>430</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="479" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12363,7 +12363,7 @@
         <v>431</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="480" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12371,7 +12371,7 @@
         <v>432</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="481" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -12379,7 +12379,7 @@
         <v>433</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="482" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12387,7 +12387,7 @@
         <v>434</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="483" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12395,7 +12395,7 @@
         <v>435</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="484" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -12403,7 +12403,7 @@
         <v>436</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="485" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12411,7 +12411,7 @@
         <v>437</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="486" spans="1:2" ht="225" x14ac:dyDescent="0.25">
@@ -12419,7 +12419,7 @@
         <v>438</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="487" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -12427,7 +12427,7 @@
         <v>439</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="488" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -12435,7 +12435,7 @@
         <v>454</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="489" spans="1:2" ht="270" x14ac:dyDescent="0.25">
@@ -12443,7 +12443,7 @@
         <v>462</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="490" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -12451,7 +12451,7 @@
         <v>463</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="491" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -12459,7 +12459,7 @@
         <v>464</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="492" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -12467,7 +12467,7 @@
         <v>544</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="493" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -12475,7 +12475,7 @@
         <v>620</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="494" spans="1:2" ht="255" x14ac:dyDescent="0.25">
@@ -12483,7 +12483,7 @@
         <v>484</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="495" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12491,7 +12491,7 @@
         <v>485</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="496" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12499,7 +12499,7 @@
         <v>486</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="497" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12507,7 +12507,7 @@
         <v>487</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="498" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12515,7 +12515,7 @@
         <v>488</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="499" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12523,7 +12523,7 @@
         <v>489</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="500" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12531,7 +12531,7 @@
         <v>490</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="501" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12539,7 +12539,7 @@
         <v>491</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="502" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12547,7 +12547,7 @@
         <v>492</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="503" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -12555,7 +12555,7 @@
         <v>493</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="504" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12563,7 +12563,7 @@
         <v>494</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="505" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12571,7 +12571,7 @@
         <v>495</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="506" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -12579,7 +12579,7 @@
         <v>496</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="507" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12587,7 +12587,7 @@
         <v>497</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="508" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12595,7 +12595,7 @@
         <v>498</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="509" spans="1:2" ht="255" x14ac:dyDescent="0.25">
@@ -12603,7 +12603,7 @@
         <v>585</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="510" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12611,7 +12611,7 @@
         <v>586</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="511" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12619,7 +12619,7 @@
         <v>499</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="512" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12627,7 +12627,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="513" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -12635,7 +12635,7 @@
         <v>420</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="514" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12659,7 +12659,7 @@
         <v>267</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="517" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12667,7 +12667,7 @@
         <v>268</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="518" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12675,7 +12675,7 @@
         <v>269</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="519" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12683,7 +12683,7 @@
         <v>270</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="520" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12691,7 +12691,7 @@
         <v>271</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="521" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12699,7 +12699,7 @@
         <v>272</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="522" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12707,7 +12707,7 @@
         <v>273</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="523" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12715,7 +12715,7 @@
         <v>274</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="524" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12723,7 +12723,7 @@
         <v>275</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="525" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12731,7 +12731,7 @@
         <v>276</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="526" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -12739,7 +12739,7 @@
         <v>277</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="527" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12771,7 +12771,7 @@
         <v>315</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="531" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12819,7 +12819,7 @@
         <v>280</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="537" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12827,7 +12827,7 @@
         <v>281</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="538" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -12843,7 +12843,7 @@
         <v>283</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="540" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12851,7 +12851,7 @@
         <v>284</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="541" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12859,7 +12859,7 @@
         <v>285</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="542" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12867,7 +12867,7 @@
         <v>286</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="543" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12915,7 +12915,7 @@
         <v>292</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="549" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12923,7 +12923,7 @@
         <v>293</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="550" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12931,7 +12931,7 @@
         <v>294</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="551" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12939,7 +12939,7 @@
         <v>295</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="552" spans="1:2" ht="240" x14ac:dyDescent="0.25">
@@ -12947,7 +12947,7 @@
         <v>296</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="553" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12955,7 +12955,7 @@
         <v>297</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="554" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -12963,7 +12963,7 @@
         <v>352</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="555" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -12971,7 +12971,7 @@
         <v>364</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="556" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -12979,7 +12979,7 @@
         <v>365</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="557" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -12987,7 +12987,7 @@
         <v>298</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="558" spans="1:2" ht="210" x14ac:dyDescent="0.25">
@@ -12995,7 +12995,7 @@
         <v>363</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="559" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -13003,7 +13003,7 @@
         <v>299</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="560" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -13011,7 +13011,7 @@
         <v>353</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="561" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -13027,7 +13027,7 @@
         <v>300</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="563" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -13035,7 +13035,7 @@
         <v>301</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="564" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -13043,7 +13043,7 @@
         <v>302</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="565" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -13051,7 +13051,7 @@
         <v>303</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="566" spans="1:2" ht="165" x14ac:dyDescent="0.25">
@@ -13059,7 +13059,7 @@
         <v>362</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="567" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -13067,7 +13067,7 @@
         <v>304</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="568" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -13075,7 +13075,7 @@
         <v>360</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="569" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -13091,7 +13091,7 @@
         <v>513</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="571" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -13099,7 +13099,7 @@
         <v>305</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="572" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -13107,7 +13107,7 @@
         <v>357</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="573" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -13115,7 +13115,7 @@
         <v>358</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="574" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -13131,7 +13131,7 @@
         <v>514</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="576" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -13139,7 +13139,7 @@
         <v>306</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="577" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -13147,7 +13147,7 @@
         <v>351</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="578" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -13155,7 +13155,7 @@
         <v>354</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="579" spans="1:2" ht="405" x14ac:dyDescent="0.25">
@@ -13163,7 +13163,7 @@
         <v>307</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="580" spans="1:2" ht="375" x14ac:dyDescent="0.25">
@@ -13171,7 +13171,7 @@
         <v>311</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="581" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -13195,7 +13195,7 @@
         <v>348</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="584" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -13203,7 +13203,7 @@
         <v>515</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="585" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -13211,7 +13211,7 @@
         <v>325</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="586" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -13235,7 +13235,7 @@
         <v>650</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="589" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -13243,7 +13243,7 @@
         <v>652</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="590" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -13251,7 +13251,7 @@
         <v>651</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
   </sheetData>
